--- a/data/interim/law_parsing/labor/candidate_normative_sentences.xlsx
+++ b/data/interim/law_parsing/labor/candidate_normative_sentences.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,35 +446,180 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>doc_code</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>unit_ref_full</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>source_ref</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>parent_context</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>source_text</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>sentence_text</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>candidate_type</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>candidate_subtype</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>candidate_score</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>trigger_patterns</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actor_text</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>action_text</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>object_text</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>condition_text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>deadline_text</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>authority_text</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>document_text</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>exception_text</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>threshold_text</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>legal_effect_text</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>should_extract_rule</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>extraction_priority</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sentence_type</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>normative_pattern</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>subject_span</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>action_span</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>modality_span</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>condition_span</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>time_span</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>document_span</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>authority_span</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>candidate_rule_type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>candidate_type</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>normative_pattern</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>exception_text</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>authority_text</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>confidence_manual</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ns_id</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -493,36 +638,158 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DOC_08</t>
+          <t>DOC_LABOR_08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ngoai_le</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>trong_thoi_han;tru_truong_hop;dieu_kien;khong_duoc</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>prohibition</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>không được</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>deadline</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ngoai_le</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>prohibition</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>trừ trường hợp các bên có thỏa thuận khác</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>4cc1b88456c97f25</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_truong_hop; cue=prohibition,permission,deadline; high_confidence_kept; ; q=3.8000000000000003</t>
         </is>
@@ -541,36 +808,154 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DOC_08</t>
+          <t>DOC_LABOR_08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>trừ trường hợp các bên có thỏa thuận khác</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ngoai_le</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>tru_truong_hop;dieu_kien</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>prohibition</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>không được</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ngoai_le</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>prohibition</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>trừ trường hợp các bên có thỏa thuận khác</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>88e70bd3d97e722d</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_truong_hop; cue=prohibition,permission,deadline; high_confidence_kept; derived_ngoai_le; q=3.8000000000000003</t>
         </is>
@@ -589,36 +974,158 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DOC_08</t>
+          <t>DOC_LABOR_08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ngoai_le</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>tru_truong_hop;dieu_kien</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>prohibition</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>không được</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ngoai_le</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>prohibition</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>trừ trường hợp các bên có thỏa thuận khác</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>7e496233cbdfb794</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_truong_hop; cue=prohibition,permission,deadline; high_confidence_kept; derived_nguong; q=3.8000000000000003</t>
         </is>
@@ -637,36 +1144,158 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DOC_08</t>
+          <t>DOC_LABOR_08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ngoai_le</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>trong_thoi_han;tru_truong_hop;dieu_kien</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>prohibition</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>không được</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>deadline</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ngoai_le</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>prohibition</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>trừ trường hợp các bên có thỏa thuận khác</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>ba6d4263dea42022</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_truong_hop; cue=prohibition,permission,deadline; high_confidence_kept; derived_thoi_han; q=3.8000000000000003</t>
         </is>
@@ -685,32 +1314,150 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DOC_08</t>
+          <t>DOC_LABOR_08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>trường hợp các bên có thỏa thuận khác</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>dieu_kien</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>prohibition</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>không được</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>dieu_kien_ap_dung</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>prohibition</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>006b80a96ce681c3</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_truong_hop; cue=prohibition,permission,deadline; high_confidence_kept; derived_dieu_kien; q=3.8000000000000003</t>
         </is>
@@ -729,32 +1476,142 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Điều 4 khoản 3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D4_K3_S1_SS1|doc_id=DOC_LABOR_09|chapter=II|section=|article=4|clause=3|point=|lines=46-47</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Điều 4. Báo cáo sử dụng lao động</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Chương II | Điều 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Định kỳ 06 tháng, trước ngày 15 tháng 6 và hằng năm, trước ngày 15 tháng 12, Sở Lao động - Thương binh và Xã hội có trách nhiệm báo cáo Bộ Lao động - Thương binh và Xã hội về tình hình sử dụng lao động trên địa bàn thông qua Cổng Dịch vụ công Quốc gia theo Mẫu số 02/PLI Phụ lục I ban hành kèm theo Nghị định này.
+Trường hợp Sở Lao động - Thương binh và Xã hội không thể báo cáo tình hình sử dụng lao động thông qua Cổng Dịch vụ công Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Phụ lục I ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Phụ lục I ban hành kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Phụ lục I ban hành</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Phụ lục I ban hành</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>b3680e9ee8100a83</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -773,32 +1630,142 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Điều 4 khoản 3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D4_K3_S1_SS1|doc_id=DOC_LABOR_09|chapter=II|section=|article=4|clause=3|point=|lines=46-47</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Điều 4. Báo cáo sử dụng lao động</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Chương II | Điều 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Định kỳ 06 tháng, trước ngày 15 tháng 6 và hằng năm, trước ngày 15 tháng 12, Sở Lao động - Thương binh và Xã hội có trách nhiệm báo cáo Bộ Lao động - Thương binh và Xã hội về tình hình sử dụng lao động trên địa bàn thông qua Cổng Dịch vụ công Quốc gia theo Mẫu số 02/PLI Phụ lục I ban hành kèm theo Nghị định này.
+Trường hợp Sở Lao động - Thương binh và Xã hội không thể báo cáo tình hình sử dụng lao động thông qua Cổng Dịch vụ công Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Phụ lục I ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Phụ lục I ban hành</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Phụ lục I ban hành</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>ec4d4dc304021b24</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -817,32 +1784,141 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Điều 6</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D6_S1_SS1|doc_id=DOC_LABOR_09|chapter=III|section=1|article=6|clause=|point=|lines=76-77</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Điều 6. Nội dung hợp đồng lao động đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Chương III | Mục 1 | Điều 6</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Nội dung hợp đồng lao động đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ luật Lao động.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ luật Lao động.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>nguong_so_luong</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>nguong_so_luong;co_quyen</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>người lao động</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ luật Lao động.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>vốn điều lệ</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ lu</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dieu</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>permission</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>nguong_so_luong</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>người lao động</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ luật Lao động.</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>được</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>permission</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>672834fac5402427</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=permission_co_quyen; cue=permission; ; q=2.0</t>
         </is>
@@ -861,32 +1937,141 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Điều 6</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D6_S1_SS1|doc_id=DOC_LABOR_09|chapter=III|section=1|article=6|clause=|point=|lines=76-77</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Điều 6. Nội dung hợp đồng lao động đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Chương III | Mục 1 | Điều 6</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Nội dung hợp đồng lao động đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ luật Lao động.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ lu</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>nguong_so_luong</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>nguong_so_luong;co_quyen</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>người lao động</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ luật Lao động.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>vốn điều lệ</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ lu</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dieu</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>permission</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>người lao động</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ luật Lao động.</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>được</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>nguong_so_luong</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>permission</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>93f432c987409317</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=permission_co_quyen; cue=permission; derived_nguong; q=2.0</t>
         </is>
@@ -905,36 +2090,137 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Điều 16 khoản 1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D16_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=2|article=16|clause=1|point=|lines=157-157</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Điều 16. Nộp tiền ký quỹ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 2 | Điều 16</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại thực hiện nộp tiền ký quỹ theo quy định của ngân hàng nhận ký quỹ và tuân thủ quy định của pháp luật. Doanh nghiệp cho thuê lại được hưởng lãi suất từ tiền ký quỹ theo thỏa thuận với ngân hàng nhận ký quỹ và phù hợp quy định của pháp luật.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Doanh nghiệp cho thuê lại thực hiện nộp tiền ký quỹ theo quy định của ngân hàng nhận ký quỹ và tuân thủ quy định của pháp luật</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>thực hiện nộp tiền ký quỹ theo quy định của ngân hàng nhận ký quỹ và</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>tuân thủ</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>ngân hàng nhận ký quỹ</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>ngân hàng nhận ký quỹ</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>procedure</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>thu_tuc</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>duty</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ngân hàng nhận ký quỹ</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>e65014b833ad8b69</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=procedure; cue=none; ; q=1.7999999999999998</t>
         </is>
@@ -953,32 +2239,125 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Điều 18 khoản 4 điểm a</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D18_K4_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=2|article=18|clause=4|point=a|lines=180-180</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Điều 18. Rút tiền ký quỹ</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 2 | Điều 18</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>Doanh nghiệp cho thuê lại nộp 01 bộ hồ sơ quy định tại khoản 2 Điều này tại Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính;</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại nộp 01 bộ hồ sơ quy định tại khoản 2 Điều này tại Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính;</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ho_so</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>procedure</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>thu_tuc</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>duty</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>892bc387a6c2eaea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=procedure; cue=none; ; q=1.7999999999999998</t>
         </is>
@@ -997,32 +2376,145 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Điều 20 khoản 1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D20_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=2|article=20|clause=1|point=|lines=193-193</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Điều 20. Nộp bổ sung tiền ký quỹ</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 2 | Điều 20</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Trong thời hạn 30 ngày kể từ ngày rút tiền ký quỹ để thanh toán đối với trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại phải nộp bổ sung tiền ký quỹ bảo đảm quy định tại khoản 2 Điều 21 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại phải nộp bổ sung tiền ký quỹ bảo đảm quy định tại khoản 2 Điều 21 Nghị định này.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>nghia_vu</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>dieu_kien;thu_tuc</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>nộp bổ sung tiền ký quỹ bảo đảm quy định tại khoản 2 Điều 21 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>nộp bổ</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>obligation</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>nộp bổ sung tiền ký quỹ bảo đảm quy định tại khoản 2 Điều 21 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>phải</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>duty</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>nghia_vu</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>obligation</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>629ee3ac0338e98e</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=procedure; cue=obligation; ; q=3.8000000000000007</t>
         </is>
@@ -1041,32 +2533,141 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Điều 20 khoản 1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D20_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=2|article=20|clause=1|point=|lines=193-193</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Điều 20. Nộp bổ sung tiền ký quỹ</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 2 | Điều 20</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Trong thời hạn 30 ngày kể từ ngày rút tiền ký quỹ để thanh toán đối với trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại phải nộp bổ sung tiền ký quỹ bảo đảm quy định tại khoản 2 Điều 21 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>dieu_kien</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>nộp bổ sung tiền ký quỹ bảo đảm quy định tại khoản 2 Điều 21 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>obligation</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>nộp bổ sung tiền ký quỹ bảo đảm quy định tại khoản 2 Điều 21 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>phải</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>dieu_kien_ap_dung</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>obligation</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>1471daf35196c125</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=procedure; cue=obligation; derived_dieu_kien; q=3.8000000000000007</t>
         </is>
@@ -1085,32 +2686,141 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Điều 23 khoản 2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D23_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=23|clause=2|point=|lines=206-206</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Điều 23. Giấy phép hoạt động cho thuê lại lao động</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 23</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Nội dung giấy phép hoạt động cho thuê lại lao động theo Mẫu số 04/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Nội dung giấy phép hoạt động cho thuê lại lao động theo Mẫu số 04/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Nội dung giấy phép hoạt động cho thuê lại lao động theo Mẫu số 04/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Nội dung giấy phép hoạt động cho thuê lại lao động theo Mẫu số 04/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>f3ab68c6ede863cf</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -1129,32 +2839,141 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Điều 23 khoản 2</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D23_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=23|clause=2|point=|lines=206-206</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Điều 23. Giấy phép hoạt động cho thuê lại lao động</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 23</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Nội dung giấy phép hoạt động cho thuê lại lao động theo Mẫu số 04/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Nội dung giấy phép hoạt động cho thuê lại lao động theo Mẫu số 04/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Nội dung giấy phép hoạt động cho thuê lại lao động theo Mẫu số 04/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>6ef8ce196fde7717</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -1173,32 +2992,141 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D24_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=24|clause=2|point=|lines=213-213</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Điều 24. Hồ sơ đề nghị cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 24</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>Bản lý lịch tự thuật của người đại diện theo pháp luật của doanh nghiệp theo Mẫu số 07/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Bản lý lịch tự thuật của người đại diện theo pháp luật của doanh nghiệp theo Mẫu số 07/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Bản lý lịch tự thuật của người đại diện theo pháp luật của doanh nghiệp theo Mẫu số 07/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bản lý lịch tự thuật của người đại diện theo pháp luật của doanh nghiệp theo Mẫu số 07/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>5fe938df7aa2d156</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -1217,32 +3145,141 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D24_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=24|clause=2|point=|lines=213-213</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Điều 24. Hồ sơ đề nghị cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 24</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Bản lý lịch tự thuật của người đại diện theo pháp luật của doanh nghiệp theo Mẫu số 07/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Bản lý lịch tự thuật của người đại diện theo pháp luật của doanh nghiệp theo Mẫu số 07/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bản lý lịch tự thuật của người đại diện theo pháp luật của doanh nghiệp theo Mẫu số 07/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>9580b2504ddb61b0</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -1261,32 +3298,141 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D24_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=24|clause=5|point=|lines=220-220</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Điều 24. Hồ sơ đề nghị cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 24</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>Giấy chứng nhận tiền ký quỹ hoạt động cho thuê lại lao động theo Mẫu số 01/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận tiền ký quỹ hoạt động cho thuê lại lao động theo Mẫu số 01/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận tiền ký quỹ hoạt động cho thuê lại lao động theo Mẫu số 01/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận tiền ký quỹ hoạt động cho thuê lại lao động theo Mẫu số 01/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>cfa771b0b39e5151</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -1305,32 +3451,141 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 5</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D24_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=24|clause=5|point=|lines=220-220</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Điều 24. Hồ sơ đề nghị cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 24</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận tiền ký quỹ hoạt động cho thuê lại lao động theo Mẫu số 01/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận tiền ký quỹ hoạt động cho thuê lại lao động theo Mẫu số 01/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận tiền ký quỹ hoạt động cho thuê lại lao động theo Mẫu số 01/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>b292429df85071f3</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -1349,32 +3604,129 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Điều 25 khoản 1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D25_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=25|clause=1|point=|lines=222-222</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Điều 25. Trình tự, thủ tục cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 25</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp gửi một bộ hồ sơ theo quy định tại Điều 24 Nghị định này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính để đề nghị cấp giấy phép.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>Doanh nghiệp gửi một bộ hồ sơ theo quy định tại Điều 24 Nghị định này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính để đề nghị</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>ho_so</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>gửi một bộ hồ sơ theo quy định tại Điều 24 Nghị định này đến Sở Lao</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>động -</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>procedure</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>thu_tuc</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>duty</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>99ad86c90735a3f6</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=procedure; cue=none; ; q=1.7999999999999998</t>
         </is>
@@ -1393,32 +3745,141 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Điều 26 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D26_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=26|clause=2|point=a|lines=239-239</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Điều 26. Gia hạn giấy phép</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 26</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>Văn bản đề nghị gia hạn giấy phép của doanh nghiệp theo Mẫu số 05/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị gia hạn giấy phép của doanh nghiệp theo Mẫu số 05/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị gia hạn giấy phép của doanh nghiệp theo Mẫu số 05/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị gia hạn giấy phép của doanh nghiệp theo Mẫu số 05/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>7c3ea369d97ba78f</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -1437,32 +3898,141 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Điều 26 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D26_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=26|clause=2|point=a|lines=239-239</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Điều 26. Gia hạn giấy phép</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 26</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị gia hạn giấy phép của doanh nghiệp theo Mẫu số 05/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>kèm theo Nghị định này</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị gia hạn giấy phép của doanh nghiệp theo Mẫu số 05/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị gia hạn giấy phép của doanh nghiệp theo Mẫu số 05/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>0206f80dabbaad08</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -1481,32 +4051,125 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Điều 26 khoản 3 điểm a</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D26_K3_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=26|clause=3|point=a|lines=243-243</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Điều 26. Gia hạn giấy phép</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 26</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp gửi một bộ hồ sơ theo quy định tại khoản 2 Điều này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính để đề nghị gia hạn giấy phép. Sau khi kiểm tra đủ giấy tờ quy định tại khoản 2 Điều này, Sở Lao động - Thương binh và Xã hội cấp giấy biên nhận ghi rõ ngày, tháng, năm nhận hồ sơ đề nghị gia hạn giấy phép;</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>Doanh nghiệp gửi một bộ hồ sơ theo quy định tại khoản 2 Điều này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính để đề nghị gia hạn giấy phép</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>ho_so</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>gửi một bộ hồ sơ theo quy định tại khoản 2 Điều này đến Sở Lao động -</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>procedure</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>thu_tuc</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>fd888efe39c7b02a</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=procedure; cue=none; ; q=1.7999999999999998</t>
         </is>
@@ -1525,32 +4188,125 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Điều 27 khoản 3 điểm a</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D27_K3_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=27|clause=3|point=a|lines=260-260</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Điều 27. Cấp lại giấy phép</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 27</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp gửi một bộ hồ sơ theo quy định tại khoản 2 Điều này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính để đề nghị cấp lại giấy phép. Sau khi kiểm tra đủ giấy tờ quy định tại khoản 2 Điều này, Sở Lao động - Thương binh và Xã hội cấp giấy biên nhận ghi rõ ngày, tháng, năm nhận hồ sơ đề nghị gia hạn giấy phép;</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>Doanh nghiệp gửi một bộ hồ sơ theo quy định tại khoản 2 Điều này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính để đề nghị</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>ho_so</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>gửi một bộ hồ sơ theo quy định tại khoản 2 Điều này đến Sở Lao động -</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>procedure</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>thu_tuc</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>duty</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>ae67012c114d4560</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=procedure; cue=none; ; q=1.7999999999999998</t>
         </is>
@@ -1569,32 +4325,125 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Điều 27 khoản 4 điểm b</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D27_K4_B_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=27|clause=4|point=b|lines=265-265</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Điều 27. Cấp lại giấy phép</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 27</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp gửi một bộ hồ sơ quy định tại điểm a khoản này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính mới để đề nghị cấp giấy phép. Sở Lao động - Thương binh và Xã hội cấp giấy biên nhận ghi rõ ngày, tháng, năm nhận hồ sơ khi hồ sơ có đủ các giấy tờ quy định tại điểm a khoản này;</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>Doanh nghiệp gửi một bộ hồ sơ quy định tại điểm a khoản này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính mới để đề nghị</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ho_so</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>gửi một bộ hồ sơ quy định tại điểm a khoản này đến Sở Lao động - Thương</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>procedure</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>thu_tuc</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>duty</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>3762912dc5b735b0</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=procedure; cue=none; ; q=1.7999999999999998</t>
         </is>
@@ -1613,32 +4462,125 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=1|point=|lines=280-280</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại bị thu hồi giấy phép trong các trường hợp sau đây:</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>Doanh nghiệp cho thuê lại bị thu hồi giấy phép trong các</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>bị thu hồi giấy phép trong các</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>legal_effect</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ket_qua_phap_ly</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>duty</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>44bef16f3ceade4a</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=legal_effect; cue=none; ; q=0.6</t>
         </is>
@@ -1657,32 +4599,125 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=1|point=|lines=280-280</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại bị thu hồi giấy phép trong các trường hợp sau đây:</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>bị thu hồi giấy phép trong các</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>bị thu hồi giấy phép trong các</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>legal_effect</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ket_qua_phap_ly</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>duty</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>bcb372e206cedf70</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=legal_effect; cue=none; derived_ket_qua; q=0.6</t>
         </is>
@@ -1701,32 +4736,149 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=a|lines=282-282</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ket_qua_phap_ly</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>176ac47bbdf08173</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -1745,32 +4897,149 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=a|lines=282-282</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr">
         <is>
           <t>legal_effect</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ket_qua_phap_ly</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>fc282de9d20c775d</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ket_qua; q=4.6000000000000005</t>
         </is>
@@ -1789,32 +5058,145 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=a|lines=282-282</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>kèm theo Nghị định này</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>2e5382269df132fe</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -1833,32 +5215,141 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm c</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_C_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=c|lines=284-284</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>Báo cáo tình hình hoạt động cho thuê lại lao động của doanh nghiệp theo Mẫu số 09/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Báo cáo tình hình hoạt động cho thuê lại lao động của doanh nghiệp theo Mẫu số 09/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Báo cáo tình hình hoạt động cho thuê lại lao động của doanh nghiệp theo Mẫu số 09/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Báo cáo tình hình hoạt động cho thuê lại lao động của doanh nghiệp theo Mẫu số 09/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>24a186ac0b7704bb</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -1877,32 +5368,141 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm c</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_C_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=c|lines=284-284</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Báo cáo tình hình hoạt động cho thuê lại lao động của doanh nghiệp theo Mẫu số 09/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>kèm theo Nghị định này</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Báo cáo tình hình hoạt động cho thuê lại lao động của doanh nghiệp theo Mẫu số 09/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Báo cáo tình hình hoạt động cho thuê lại lao động của doanh nghiệp theo Mẫu số 09/PLIII Phụ lục III ban hành</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Nghị định này</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>c52ee886fc6b9836</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -1921,32 +5521,125 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 3 điểm a</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K3_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=3|point=a|lines=287-287</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>Doanh nghiệp gửi một bộ hồ sơ theo quy định tại khoản 2 Điều này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính;</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp gửi một bộ hồ sơ theo quy định tại khoản 2 Điều này đến Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính;</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ho_so</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>gửi một bộ hồ sơ theo quy định tại khoản 2 Điều này đến Sở Lao động -</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>procedure</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>thu_tuc</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>duty</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>eeb9033c8ba6c25f</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=procedure; cue=none; ; q=1.7999999999999998</t>
         </is>
@@ -1965,36 +5658,153 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 5</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=5|point=|lines=294-294</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>Doanh nghiệp cho thuê lại không được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại không được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>thoi_han</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>trong_thoi_han;ket_qua_phap_ly;khong_duoc</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>cấp giấy phép trong thời hạn 05 năm</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>prohibition</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>không được</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>deadline</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>thoi_han</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>prohibition</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>cấp giấy phép</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>852fe6f60963b991</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=legal_effect; cue=prohibition,permission,deadline,authority; high_confidence_kept; ; q=3.8000000000000003</t>
         </is>
@@ -2013,36 +5823,149 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 5</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=5|point=|lines=294-294</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại không được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>nguong_so_luong</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>prohibition</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>không được</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>nguong_so_luong</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>prohibition</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>cấp giấy phép</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>6978812b8f465e19</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=legal_effect; cue=prohibition,permission,deadline,authority; high_confidence_kept; derived_nguong; q=3.8000000000000003</t>
         </is>
@@ -2061,36 +5984,153 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 5</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=5|point=|lines=294-294</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại không được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>trong_thoi_han;ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>cấp giấy phép trong thời hạn 05 năm</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>prohibition</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>không được</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
         <is>
           <t>legal_effect</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>ket_qua_phap_ly</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>prohibition</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>cấp giấy phép</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>3f3665e21e437ce4</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=legal_effect; cue=prohibition,permission,deadline,authority; high_confidence_kept; derived_ket_qua; q=3.8000000000000003</t>
         </is>
@@ -2109,36 +6149,149 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 5</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=5|point=|lines=294-294</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại không được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>trong_thoi_han;ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>rat_cao</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>prohibition</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>không được</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
         <is>
           <t>deadline</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>ket_qua_phap_ly</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>prohibition</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>cấp giấy phép</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>1efa4aa10560b18c</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=legal_effect; cue=prohibition,permission,deadline,authority; high_confidence_kept; derived_thoi_han; q=3.8000000000000003</t>
         </is>
@@ -2157,32 +6310,129 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Điều 31 khoản 2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D31_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=4|article=31|clause=2|point=|lines=302-302</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Điều 31. Trách nhiệm của doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 4 | Điều 31</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Định kỳ 06 tháng và hằng năm, báo cáo tình hình hoạt động cho thuê lại lao động theo Mẫu số 09/PLIII Phụ lục III ban hành kèm theo Nghị định này, gửi Chủ tịch Ủy ban nhân dân cấp tỉnh, Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính; đồng thời báo cáo Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đến hoạt động cho thuê lại lao động về tình hình hoạt động cho thuê lại lao động trên địa bàn đó đối với trường hợp doanh nghiệp cho thuê lại sang địa bàn cấp tỉnh khác hoạt động. Báo cáo 06 tháng gửi trước ngày 20 tháng 6 và báo cáo năm gửi trước ngày 20 tháng 12.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>doanh nghiệp đến hoạt động cho thuê lại lao động về tình hình hoạt động cho thuê lại lao động trên địa bàn đó đối với trường hợp doanh nghiệp cho thuê lại sang địa bàn</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>dieu_kien</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>trường hợp doanh nghiệp cho thuê lại sang địa bàn</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>dieu_kien_ap_dung</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>trường hợp doanh nghiệp cho thuê lại sang địa bàn</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>674b7e805ab6927b</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_truong_hop; cue=none; ; q=1.7999999999999998</t>
         </is>
@@ -2201,32 +6451,129 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Điều 31 khoản 2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D31_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=4|article=31|clause=2|point=|lines=302-302</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Điều 31. Trách nhiệm của doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 4 | Điều 31</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Định kỳ 06 tháng và hằng năm, báo cáo tình hình hoạt động cho thuê lại lao động theo Mẫu số 09/PLIII Phụ lục III ban hành kèm theo Nghị định này, gửi Chủ tịch Ủy ban nhân dân cấp tỉnh, Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính; đồng thời báo cáo Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đến hoạt động cho thuê lại lao động về tình hình hoạt động cho thuê lại lao động trên địa bàn đó đối với trường hợp doanh nghiệp cho thuê lại sang địa bàn cấp tỉnh khác hoạt động. Báo cáo 06 tháng gửi trước ngày 20 tháng 6 và báo cáo năm gửi trước ngày 20 tháng 12.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>trường hợp doanh nghiệp cho thuê lại sang địa bàn</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>dieu_kien</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>trường hợp doanh nghiệp cho thuê lại sang địa bàn</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>dieu_kien_ap_dung</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>trường hợp doanh nghiệp cho thuê lại sang địa bàn</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>c39c256f76068cf0</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_truong_hop; cue=none; derived_dieu_kien; q=1.7999999999999998</t>
         </is>
@@ -2245,32 +6592,141 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Điều 85 khoản 1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D85_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IX|section=3|article=85|clause=1|point=|lines=776-776</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Điều 85. Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục tại nơi làm việc</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Chương IX | Mục 3 | Điều 85</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục trong nội quy lao động hoặc bằng phụ lục ban hành kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau:</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục trong nội quy lao động hoặc bằng phụ lục ban hành kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau:</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục trong nội quy lao động hoặc bằng phụ lục ban hành</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục trong nội quy lao động hoặc bằng phụ lục ban hành</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>20b562defdaa59c4</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -2289,32 +6745,141 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Điều 85 khoản 1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D85_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IX|section=3|article=85|clause=1|point=|lines=776-776</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Điều 85. Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục tại nơi làm việc</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Chương IX | Mục 3 | Điều 85</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục trong nội quy lao động hoặc bằng phụ lục ban hành kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau:</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục trong nội quy lao động hoặc bằng phụ lục ban hành</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục trong nội quy lao động hoặc bằng phụ lục ban hành</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>6f583e2c51f1bee6</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -2333,36 +6898,137 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DOC_10</t>
+          <t>DOC_LABOR_10</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>bao_hiem_xa_hoi_41_2024_QH15</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Điều 17 khoản 2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>unit=UNIT_BAO_HIEM_XA_HOI_41_2_D17_K2_S1_SS1|doc_id=DOC_LABOR_10|chapter=II|section=2|article=17|clause=2|point=|lines=199-199</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Điều 17. Quyền hạn của cơ quan bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Chương II | Mục 2 | Điều 17</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Được cơ quan đăng ký kinh doanh, cơ quan cấp giấy chứng nhận hoạt động hoặc giấy phép hoạt động kết nối, chia sẻ thông tin hoặc cung cấp bản sao giấy phép hoạt động, giấy chứng nhận hoạt động hoặc giấy chứng nhận đăng ký doanh nghiệp, hợp tác xã, hộ kinh doanh để rà soát, kiểm tra việc thực hiện đăng ký tham gia bảo hiểm xã hội bắt buộc đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>doanh nghiệp, hợp tác xã, hộ kinh doanh để rà soát, kiểm tra việc thực hiện đăng ký tham gia bảo hiểm xã hội bắt buộc đối với doanh nghiệp, tổ chức thành lập mới.</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>dieu_kien;dang_ky</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>dieu_kien_ap_dung</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>bảo hiểm xã hội</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>20cabea5c3bdee3b</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_doi_voi; cue=none; ; q=1.7999999999999998</t>
         </is>
@@ -2381,36 +7047,137 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DOC_10</t>
+          <t>DOC_LABOR_10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>bao_hiem_xa_hoi_41_2024_QH15</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Điều 17 khoản 2</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>unit=UNIT_BAO_HIEM_XA_HOI_41_2_D17_K2_S1_SS1|doc_id=DOC_LABOR_10|chapter=II|section=2|article=17|clause=2|point=|lines=199-199</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Điều 17. Quyền hạn của cơ quan bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Chương II | Mục 2 | Điều 17</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Được cơ quan đăng ký kinh doanh, cơ quan cấp giấy chứng nhận hoạt động hoặc giấy phép hoạt động kết nối, chia sẻ thông tin hoặc cung cấp bản sao giấy phép hoạt động, giấy chứng nhận hoạt động hoặc giấy chứng nhận đăng ký doanh nghiệp, hợp tác xã, hộ kinh doanh để rà soát, kiểm tra việc thực hiện đăng ký tham gia bảo hiểm xã hội bắt buộc đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>đối với doanh nghiệp, tổ chức thành lập mới.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>dieu_kien</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>dieu_kien_ap_dung</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>bảo hiểm xã hội</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>cd84fdf685fec284</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_doi_voi; cue=none; derived_dieu_kien; q=1.7999999999999998</t>
         </is>
@@ -2429,36 +7196,153 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DOC_10</t>
+          <t>DOC_LABOR_10</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>bao_hiem_xa_hoi_41_2024_QH15</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Điều 27 khoản 1 điểm a</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>unit=UNIT_BAO_HIEM_XA_HOI_41_2_D27_K1_A_S1_SS1|doc_id=DOC_LABOR_10|chapter=IV|section=1|article=27|clause=1|point=a|lines=293-293</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Điều 27. Hồ sơ đăng ký tham gia bảo hiểm xã hội bắt buộc và bảo hiểm xã hội tự nguyện</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 1 | Điều 27</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>Tờ khai đăng ký tham gia bảo hiểm xã hội của người sử dụng lao động kèm theo danh sách người lao động tham gia bảo hiểm xã hội;</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Tờ khai đăng ký tham gia bảo hiểm xã hội của người sử dụng lao động kèm theo danh sách người lao động tham gia bảo hiểm xã hội;</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>kem_theo;dang_ky</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Tờ khai đăng ký tham gia bảo hiểm xã hội của người sử dụng lao động</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>danh sách</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>kèm theo danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tờ khai đăng ký tham gia bảo hiểm xã hội của người sử dụng lao động</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>kèm theo danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>bảo hiểm xã hội</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>855b31b7ad395020</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -2477,36 +7361,153 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DOC_10</t>
+          <t>DOC_LABOR_10</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>bao_hiem_xa_hoi_41_2024_QH15</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Điều 27 khoản 1 điểm a</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>unit=UNIT_BAO_HIEM_XA_HOI_41_2_D27_K1_A_S1_SS1|doc_id=DOC_LABOR_10|chapter=IV|section=1|article=27|clause=1|point=a|lines=293-293</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Điều 27. Hồ sơ đăng ký tham gia bảo hiểm xã hội bắt buộc và bảo hiểm xã hội tự nguyện</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 1 | Điều 27</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Tờ khai đăng ký tham gia bảo hiểm xã hội của người sử dụng lao động kèm theo danh sách người lao động tham gia bảo hiểm xã hội;</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>kèm theo danh sách người lao động tham gia bảo hiểm xã hội</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Tờ khai đăng ký tham gia bảo hiểm xã hội của người sử dụng lao động</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>danh sách</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>kèm theo danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Tờ khai đăng ký tham gia bảo hiểm xã hội của người sử dụng lao động</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>kèm theo danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>bảo hiểm xã hội</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>53dcf2fff11693da</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -2525,32 +7526,142 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DOC_11</t>
+          <t>DOC_LABOR_11</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Điều 10 khoản 4 điểm b</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D10_K4_B_S1_SS1|doc_id=DOC_LABOR_11|chapter=II|section=|article=10|clause=4|point=b|lines=99-100</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Điều 10. Tạm dừng đóng vào quỹ hưu trí và tử tuất theo quy định tại khoản 1 và khoản 3 Điều 37 của Luật Bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Chương II | Điều 10</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Người sử dụng lao động thuộc đối tượng quy định tại điểm a khoản 2 Điều này, làm văn bản đề nghị kèm theo danh sách lao động tại thời điểm trước khi tạm dừng sản xuất, kinh doanh và tại thời điểm đề nghị; danh sách lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc.
+Người sử dụng lao động thuộc đối tượng quy định tại điểm b khoản 2 Điều này bị thiệt hại trên 50% tổng giá trị tài sản, làm văn bản đề nghị kèm theo Báo cáo kiểm kê tài sản gần nhất trước thời điểm bị thiệt hại; Biên bản kiểm kê tài sản bị thiệt hại do thiên tai, hoả hoạn, dịch bệnh, mất mùa. Trường hợp không bố trí được việc làm cho người lao động, trong đó số lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc từ 50% trở lên so với tổng số lao động có mặt trước khi thiên tai, hỏa hoạn, dịch bệnh, mất mùa thì làm văn bản đề nghị kèm theo danh sách lao động tại thời điểm trước khi thiên tai, hỏa hoạn, dịch bệnh, mất mùa và tại thời điểm đề nghị; danh sách lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc;</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>Người sử dụng lao động thuộc đối tượng quy định tại điểm a khoản 2 Điều này, làm văn bản đề nghị kèm theo danh sách lao động tại thời điểm trước</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Người sử dụng lao động thuộc đối tượng quy định tại điểm a khoản 2 Điều này, làm văn bản đề nghị</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>kèm theo danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Người sử dụng lao động thuộc đối tượng quy định tại điểm a khoản 2 Điều này, làm văn bản đề nghị</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>kèm theo danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>f058adb6af46a61e</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -2569,32 +7680,142 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DOC_11</t>
+          <t>DOC_LABOR_11</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Điều 10 khoản 4 điểm b</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D10_K4_B_S1_SS1|doc_id=DOC_LABOR_11|chapter=II|section=|article=10|clause=4|point=b|lines=99-100</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Điều 10. Tạm dừng đóng vào quỹ hưu trí và tử tuất theo quy định tại khoản 1 và khoản 3 Điều 37 của Luật Bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Chương II | Điều 10</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Người sử dụng lao động thuộc đối tượng quy định tại điểm a khoản 2 Điều này, làm văn bản đề nghị kèm theo danh sách lao động tại thời điểm trước khi tạm dừng sản xuất, kinh doanh và tại thời điểm đề nghị; danh sách lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc.
+Người sử dụng lao động thuộc đối tượng quy định tại điểm b khoản 2 Điều này bị thiệt hại trên 50% tổng giá trị tài sản, làm văn bản đề nghị kèm theo Báo cáo kiểm kê tài sản gần nhất trước thời điểm bị thiệt hại; Biên bản kiểm kê tài sản bị thiệt hại do thiên tai, hoả hoạn, dịch bệnh, mất mùa. Trường hợp không bố trí được việc làm cho người lao động, trong đó số lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc từ 50% trở lên so với tổng số lao động có mặt trước khi thiên tai, hỏa hoạn, dịch bệnh, mất mùa thì làm văn bản đề nghị kèm theo danh sách lao động tại thời điểm trước khi thiên tai, hỏa hoạn, dịch bệnh, mất mùa và tại thời điểm đề nghị; danh sách lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc;</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>kèm theo danh sách lao động tại thời điểm trước</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Người sử dụng lao động thuộc đối tượng quy định tại điểm a khoản 2 Điều này, làm văn bản đề nghị</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>kèm theo danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Người sử dụng lao động thuộc đối tượng quy định tại điểm a khoản 2 Điều này, làm văn bản đề nghị</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>kèm theo danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>a834dcf75ee7450e</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -2613,32 +7834,141 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DOC_11</t>
+          <t>DOC_LABOR_11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Điều 12 khoản 1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D12_K1_S1_SS1|doc_id=DOC_LABOR_11|chapter=III|section=1|article=12|clause=1|point=|lines=122-122</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Điều 12. Điều kiện hưởng lương hưu</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Chương III | Mục 1 | Điều 12</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>Công việc khai thác than trong hầm lò theo Phụ lục I ban hành kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Công việc khai thác than trong hầm lò theo Phụ lục I ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Công việc khai thác than trong hầm lò theo Phụ lục I ban hành</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Công việc khai thác than trong hầm lò theo Phụ lục I ban hành</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>4cc62fc39d793127</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -2657,32 +7987,141 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DOC_11</t>
+          <t>DOC_LABOR_11</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Điều 12 khoản 1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D12_K1_S1_SS1|doc_id=DOC_LABOR_11|chapter=III|section=1|article=12|clause=1|point=|lines=122-122</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Điều 12. Điều kiện hưởng lương hưu</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Chương III | Mục 1 | Điều 12</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Công việc khai thác than trong hầm lò theo Phụ lục I ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>kèm theo Nghị định này.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Công việc khai thác than trong hầm lò theo Phụ lục I ban hành</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>khoan</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Công việc khai thác than trong hầm lò theo Phụ lục I ban hành</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>6dffe53c256d474c</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
@@ -2701,36 +8140,157 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DOC_11</t>
+          <t>DOC_LABOR_11</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 1 điểm c</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D28_K1_C_S1_SS1|doc_id=DOC_LABOR_11|chapter=V|section=|article=28|clause=1|point=c|lines=309-309</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Điều 28. Căn cứ xác nhận thời gian đóng bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Chương V | Điều 28</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Thông báo của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể đối với trường hợp đang làm thủ tục giải thể;</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>Thông báo của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể đối với trường hợp đang làm</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>thu_tuc</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>thong_bao</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>co_quan;dieu_kien;dang_ky;thong_bao;thu_tuc</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>thủ tục</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>trường hợp đang làm</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>procedure</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Thông báo</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>trường hợp đang làm</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
         <is>
           <t>authority_action</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>thu_tuc</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>0f4cbbfaa5a8526d</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_truong_hop; cue=authority; ; q=2.5999999999999996</t>
         </is>
@@ -2749,36 +8309,149 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DOC_11</t>
+          <t>DOC_LABOR_11</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 1 điểm c</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D28_K1_C_S1_SS1|doc_id=DOC_LABOR_11|chapter=V|section=|article=28|clause=1|point=c|lines=309-309</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Điều 28. Căn cứ xác nhận thời gian đóng bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Chương V | Điều 28</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Thông báo của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể đối với trường hợp đang làm thủ tục giải thể;</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>trường hợp đang làm</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>dieu_kien</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>trường hợp đang làm</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>procedure</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>Thông báo</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>trường hợp đang làm</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>dieu_kien_ap_dung</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>f994588b89037127</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=condition_truong_hop; cue=authority; derived_dieu_kien; q=2.5999999999999996</t>
         </is>
@@ -2797,32 +8470,142 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DOC_11</t>
+          <t>DOC_LABOR_11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Điều 36 khoản 1 điểm b</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D36_K1_B_S1_SS1|doc_id=DOC_LABOR_11|chapter=VI|section=|article=36|clause=1|point=b|lines=408-409</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Điều 36. Hồ sơ đề nghị tính thời gian công tác đối với người lao động đi hợp tác lao động trước ngày 01 tháng 01 năm 1995</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Chương VI | Điều 36</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Bản chính “Thông báo chuyển trả” hoặc “Quyết định chuyển trả” của Cục Hợp tác quốc tế về lao động (nay là Cục Quản lý lao động ngoài nước) cấp.
+Trường hợp không còn bản chính “Thông báo chuyển trả” hoặc “Quyết định chuyển trả” thì phải có Giấy xác nhận về thời gian đi hợp tác lao động để giải quyết chế độ bảo hiểm xã hội của Cục Quản lý lao động ngoài nước trên cơ sở đơn đề nghị của người lao động (theo Mẫu số 01 và số 02 Phụ lục II ban hành kèm theo Nghị định này);</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
           <t>Cục Quản lý lao động ngoài nước trên cơ sở đơn đề nghị của người lao động (theo Mẫu số 01 và số 02 Phụ lục II ban hành kèm theo Nghị định này);</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Cục Quản lý lao động ngoài nước trên cơ sở đơn đề nghị của người lao động (theo Mẫu số 01 và số 02 Phụ lục II ban hành</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Nghị định này)</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này)</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Cục Quản lý lao động ngoài nước trên cơ sở đơn đề nghị của người lao động (theo Mẫu số 01 và số 02 Phụ lục II ban hành</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Nghị định này)</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này)</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>f758c2bc6d972659</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; ; q=4.6000000000000005</t>
         </is>
@@ -2841,32 +8624,142 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DOC_11</t>
+          <t>DOC_LABOR_11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Điều 36 khoản 1 điểm b</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D36_K1_B_S1_SS1|doc_id=DOC_LABOR_11|chapter=VI|section=|article=36|clause=1|point=b|lines=408-409</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Điều 36. Hồ sơ đề nghị tính thời gian công tác đối với người lao động đi hợp tác lao động trước ngày 01 tháng 01 năm 1995</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Chương VI | Điều 36</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Bản chính “Thông báo chuyển trả” hoặc “Quyết định chuyển trả” của Cục Hợp tác quốc tế về lao động (nay là Cục Quản lý lao động ngoài nước) cấp.
+Trường hợp không còn bản chính “Thông báo chuyển trả” hoặc “Quyết định chuyển trả” thì phải có Giấy xác nhận về thời gian đi hợp tác lao động để giải quyết chế độ bảo hiểm xã hội của Cục Quản lý lao động ngoài nước trên cơ sở đơn đề nghị của người lao động (theo Mẫu số 01 và số 02 Phụ lục II ban hành kèm theo Nghị định này);</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
           <t>kèm theo Nghị định này)</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>kem_theo</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Cục Quản lý lao động ngoài nước trên cơ sở đơn đề nghị của người lao động (theo Mẫu số 01 và số 02 Phụ lục II ban hành</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Nghị định này)</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này)</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>can_nhac</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>thap</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>diem</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>dossier</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Cục Quản lý lao động ngoài nước trên cơ sở đơn đề nghị của người lao động (theo Mẫu số 01 và số 02 Phụ lục II ban hành</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Nghị định này)</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>kèm theo</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này)</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>document_requirement</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>thanh_phan_ho_so</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>dossier</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>dd7c19a0dc8575ff</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
         <is>
           <t>split=trigger_window; matched=dossier_kem_theo; cue=document; derived_ho_so; q=4.6000000000000005</t>
         </is>
